--- a/NA_spotify.xlsx
+++ b/NA_spotify.xlsx
@@ -450,7 +450,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -480,7 +480,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1681</v>
+        <v>1886</v>
       </c>
     </row>
     <row r="7">
@@ -596,27 +596,27 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>duration_ms</t>
+          <t>track_album_release_date_year</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>1886</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>track_album_release_date_year</t>
+          <t>playlist_count_per_song</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1681</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>playlist_count_per_song</t>
+          <t>duration_minutes</t>
         </is>
       </c>
       <c r="B20" t="n">

--- a/NA_spotify.xlsx
+++ b/NA_spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -606,7 +606,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>playlist_count_per_song</t>
+          <t>loudness_shifted</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -616,7 +616,7 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>duration_minutes</t>
+          <t>playlist_count_per_song</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -626,10 +626,20 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
+          <t>duration_minutes</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
           <t>playlist_genre_count_per_song</t>
         </is>
       </c>
-      <c r="B21" t="n">
+      <c r="B22" t="n">
         <v>0</v>
       </c>
     </row>

--- a/NA_spotify.xlsx
+++ b/NA_spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -606,7 +606,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>loudness_shifted</t>
+          <t>playlist_count_per_song</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -616,7 +616,7 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>playlist_count_per_song</t>
+          <t>duration_minutes</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -626,20 +626,10 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>duration_minutes</t>
+          <t>playlist_genre_count_per_song</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>playlist_genre_count_per_song</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
         <v>0</v>
       </c>
     </row>

--- a/NA_spotify.xlsx
+++ b/NA_spotify.xlsx
@@ -450,7 +450,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -480,7 +480,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1886</v>
+        <v>1681</v>
       </c>
     </row>
     <row r="7">
@@ -600,7 +600,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1886</v>
+        <v>1681</v>
       </c>
     </row>
     <row r="19">

--- a/NA_spotify.xlsx
+++ b/NA_spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -596,27 +596,27 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>track_album_release_date_year</t>
+          <t>track_album_release_date_converted</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1681</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>playlist_count_per_song</t>
+          <t>track_album_release_date_year</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>1681</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>duration_minutes</t>
+          <t>playlist_count_per_song</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -626,10 +626,20 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
+          <t>duration_minutes</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
           <t>playlist_genre_count_per_song</t>
         </is>
       </c>
-      <c r="B21" t="n">
+      <c r="B22" t="n">
         <v>0</v>
       </c>
     </row>
